--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2020_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2020_nuble.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:16</t>
+    <t xml:space="preserve">2026-09-24 01:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -840,7 +840,7 @@
         <v>0.24</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.07</v>
@@ -860,10 +860,10 @@
         <v>21</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.14</v>
@@ -886,7 +886,7 @@
         <v>0.24</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.07</v>
@@ -909,10 +909,10 @@
         <v>0.17</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2020_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:06</t>
+    <t xml:space="preserve">2026-10-01 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -515,7 +515,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="31.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2020_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_peringrmin_a_2020_nuble.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:18</t>
+    <t xml:space="preserve">2026-10-05 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
